--- a/templates/物品导入模板_items_import_template.xlsx
+++ b/templates/物品导入模板_items_import_template.xlsx
@@ -61,21 +61,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
-    <col min="1" max="1" width="10" customWidth="1"/>
-    <col min="2" max="2" width="19" customWidth="1"/>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="2" width="26" customWidth="1"/>
     <col min="3" max="3" width="10" customWidth="1"/>
-    <col min="4" max="4" width="19" customWidth="1"/>
-    <col min="5" max="5" width="17" customWidth="1"/>
-    <col min="6" max="6" width="17" customWidth="1"/>
-    <col min="7" max="7" width="11" customWidth="1"/>
+    <col min="4" max="4" width="27" customWidth="1"/>
+    <col min="5" max="5" width="24" customWidth="1"/>
+    <col min="6" max="6" width="24" customWidth="1"/>
+    <col min="7" max="7" width="15" customWidth="1"/>
     <col min="8" max="8" width="10" customWidth="1"/>
-    <col min="9" max="9" width="13" customWidth="1"/>
+    <col min="9" max="9" width="18" customWidth="1"/>
     <col min="10" max="10" width="10" customWidth="1"/>
-    <col min="11" max="11" width="19" customWidth="1"/>
-    <col min="12" max="12" width="23" customWidth="1"/>
-    <col min="13" max="13" width="13" customWidth="1"/>
-    <col min="14" max="14" width="13" customWidth="1"/>
-    <col min="15" max="15" width="16" customWidth="1"/>
+    <col min="11" max="11" width="25" customWidth="1"/>
+    <col min="12" max="12" width="33" customWidth="1"/>
+    <col min="13" max="13" width="18" customWidth="1"/>
+    <col min="14" max="14" width="18" customWidth="1"/>
+    <col min="15" max="15" width="18" customWidth="1"/>
+    <col min="16" max="16" width="15" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -154,6 +155,11 @@
           <t xml:space="preserve">商品条形码</t>
         </is>
       </c>
+      <c r="P1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">卫生等级</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -211,6 +217,11 @@
       <c r="O2" t="inlineStr">
         <is>
           <t xml:space="preserve">6901234567890</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A</t>
         </is>
       </c>
     </row>
